--- a/Файлы/1 курс/2 семестр/Теоретическая информатика/Лабы/09.04.25 - Лаба №5/Дима/Лаб5.xlsx
+++ b/Файлы/1 курс/2 семестр/Теоретическая информатика/Лабы/09.04.25 - Лаба №5/Дима/Лаб5.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Codespace\Файлы\1 курс\2 семестр\Теоретическая информатика\Лабы\09.04.25 - Лаба №5\Влад\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luvidmi\Desktop\gitRep\Codespace\Файлы\1 курс\2 семестр\Теоретическая информатика\Лабы\09.04.25 - Лаба №5\Дима\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{647BA7BA-3482-4C82-ADA8-AFA19863E892}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A592C5CB-F511-46B6-9E6B-31A67B9A93EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14400" yWindow="600" windowWidth="14400" windowHeight="15600" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ведомость зарплаты" sheetId="1" r:id="rId1"/>
@@ -270,8 +270,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;₽&quot;_-;\-* #,##0.00\ &quot;₽&quot;_-;_-* &quot;-&quot;??\ &quot;₽&quot;_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="_-[$€-2]\ * #,##0.00_-;\-[$€-2]\ * #,##0.00_-;_-[$€-2]\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="169" formatCode="_-* #,##0.00\ [$₽-419]_-;\-* #,##0.00\ [$₽-419]_-;_-* &quot;-&quot;??\ [$₽-419]_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-[$€-2]\ * #,##0.00_-;\-[$€-2]\ * #,##0.00_-;_-[$€-2]\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$₽-419]_-;\-* #,##0.00\ [$₽-419]_-;_-* &quot;-&quot;??\ [$₽-419]_-;_-@_-"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -384,12 +384,6 @@
   </cellStyleXfs>
   <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -401,18 +395,12 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -439,6 +427,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Денежный" xfId="1" builtinId="4"/>
@@ -544,19 +544,19 @@
                   <c:v>Начислено</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v> $33,100.00 </c:v>
+                  <c:v> 33 100,00 ₽ </c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v> $29,500.00 </c:v>
+                  <c:v> 29 500,00 ₽ </c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v> $38,700.00 </c:v>
+                  <c:v> 38 700,00 ₽ </c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v> $34,000.00 </c:v>
+                  <c:v> 34 000,00 ₽ </c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v> $33,500.00 </c:v>
+                  <c:v> 33 500,00 ₽ </c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -602,6 +602,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-020C-41E1-AC3D-D32BAFCBF88C}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -644,6 +649,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-020C-41E1-AC3D-D32BAFCBF88C}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -686,6 +696,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-020C-41E1-AC3D-D32BAFCBF88C}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="3"/>
@@ -728,6 +743,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-020C-41E1-AC3D-D32BAFCBF88C}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="4"/>
@@ -770,6 +790,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-020C-41E1-AC3D-D32BAFCBF88C}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dLbls>
             <c:spPr>
@@ -3295,418 +3320,418 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
     </row>
     <row r="3" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="4">
+      <c r="A4" s="2">
         <v>1</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="2">
         <v>22</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="3">
         <v>5600</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4" s="6">
         <f>VLOOKUP(C4,$B$23:$C$28,2)*D4</f>
         <v>560</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4" s="3">
         <f>SUM(D4:E4)</f>
         <v>6160</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="4">
+      <c r="A5" s="2">
         <v>2</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="2">
         <v>5</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="3">
         <v>9700</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="6">
         <f t="shared" ref="E5:E18" si="0">VLOOKUP(C5,$B$23:$C$28,2)*D5</f>
         <v>291</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F5" s="3">
         <f t="shared" ref="F5:F17" si="1">SUM(D5:E5)</f>
         <v>9991</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="4">
+      <c r="A6" s="2">
         <v>3</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="2">
         <v>12</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="3">
         <v>6500</v>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="6">
         <f t="shared" si="0"/>
         <v>325</v>
       </c>
-      <c r="F6" s="5">
+      <c r="F6" s="3">
         <f t="shared" si="1"/>
         <v>6825</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="4">
+      <c r="A7" s="2">
         <v>4</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="2">
         <v>9</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="3">
         <v>6800</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="6">
         <f t="shared" si="0"/>
         <v>204</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F7" s="3">
         <f t="shared" si="1"/>
         <v>7004</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="4">
+      <c r="A8" s="2">
         <v>5</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8" s="2">
         <v>3</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="3">
         <v>6800</v>
       </c>
-      <c r="E8" s="8">
+      <c r="E8" s="6">
         <f t="shared" si="0"/>
         <v>68</v>
       </c>
-      <c r="F8" s="5">
+      <c r="F8" s="3">
         <f t="shared" si="1"/>
         <v>6868</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="4">
+      <c r="A9" s="2">
         <v>6</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="2">
         <v>20</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="3">
         <v>7800</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="6">
         <f t="shared" si="0"/>
         <v>780</v>
       </c>
-      <c r="F9" s="5">
+      <c r="F9" s="3">
         <f t="shared" si="1"/>
         <v>8580</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="4">
+      <c r="A10" s="2">
         <v>7</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10" s="2">
         <v>19</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10" s="3">
         <v>9900</v>
       </c>
-      <c r="E10" s="8">
+      <c r="E10" s="6">
         <f t="shared" si="0"/>
         <v>693.00000000000011</v>
       </c>
-      <c r="F10" s="5">
+      <c r="F10" s="3">
         <f t="shared" si="1"/>
         <v>10593</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="4">
+      <c r="A11" s="2">
         <v>8</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="2">
         <v>8</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D11" s="3">
         <v>3500</v>
       </c>
-      <c r="E11" s="8">
+      <c r="E11" s="6">
         <f t="shared" si="0"/>
         <v>105</v>
       </c>
-      <c r="F11" s="5">
+      <c r="F11" s="3">
         <f t="shared" si="1"/>
         <v>3605</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="4">
+      <c r="A12" s="2">
         <v>9</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="4">
+      <c r="C12" s="2">
         <v>1</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D12" s="3">
         <v>4600</v>
       </c>
-      <c r="E12" s="8">
+      <c r="E12" s="6">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="F12" s="5">
+      <c r="F12" s="3">
         <f t="shared" si="1"/>
         <v>4646</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="4">
+      <c r="A13" s="2">
         <v>10</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="4">
+      <c r="C13" s="2">
         <v>16</v>
       </c>
-      <c r="D13" s="5">
+      <c r="D13" s="3">
         <v>10500</v>
       </c>
-      <c r="E13" s="8">
+      <c r="E13" s="6">
         <f t="shared" si="0"/>
         <v>735.00000000000011</v>
       </c>
-      <c r="F13" s="5">
+      <c r="F13" s="3">
         <f t="shared" si="1"/>
         <v>11235</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="4">
+      <c r="A14" s="2">
         <v>11</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="4">
+      <c r="C14" s="2">
         <v>17</v>
       </c>
-      <c r="D14" s="5">
+      <c r="D14" s="3">
         <v>7900</v>
       </c>
-      <c r="E14" s="8">
+      <c r="E14" s="6">
         <f t="shared" si="0"/>
         <v>553</v>
       </c>
-      <c r="F14" s="5">
+      <c r="F14" s="3">
         <f t="shared" si="1"/>
         <v>8453</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="4">
+      <c r="A15" s="2">
         <v>12</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="4">
+      <c r="C15" s="2">
         <v>8</v>
       </c>
-      <c r="D15" s="5">
+      <c r="D15" s="3">
         <v>6900</v>
       </c>
-      <c r="E15" s="8">
+      <c r="E15" s="6">
         <f t="shared" si="0"/>
         <v>207</v>
       </c>
-      <c r="F15" s="5">
+      <c r="F15" s="3">
         <f t="shared" si="1"/>
         <v>7107</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="4">
+      <c r="A16" s="2">
         <v>13</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="4">
+      <c r="C16" s="2">
         <v>29</v>
       </c>
-      <c r="D16" s="5">
+      <c r="D16" s="3">
         <v>6700</v>
       </c>
-      <c r="E16" s="8">
+      <c r="E16" s="6">
         <f t="shared" si="0"/>
         <v>1005</v>
       </c>
-      <c r="F16" s="5">
+      <c r="F16" s="3">
         <f t="shared" si="1"/>
         <v>7705</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="4">
+      <c r="A17" s="2">
         <v>14</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C17" s="4">
+      <c r="C17" s="2">
         <v>19</v>
       </c>
-      <c r="D17" s="5">
+      <c r="D17" s="3">
         <v>10200</v>
       </c>
-      <c r="E17" s="8">
+      <c r="E17" s="6">
         <f t="shared" si="0"/>
         <v>714.00000000000011</v>
       </c>
-      <c r="F17" s="5">
+      <c r="F17" s="3">
         <f t="shared" si="1"/>
         <v>10914</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="4">
+      <c r="A18" s="2">
         <v>15</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="4">
+      <c r="C18" s="2">
         <v>22</v>
       </c>
-      <c r="D18" s="5">
+      <c r="D18" s="3">
         <v>7900</v>
       </c>
-      <c r="E18" s="8">
+      <c r="E18" s="6">
         <f t="shared" si="0"/>
         <v>790</v>
       </c>
-      <c r="F18" s="5">
+      <c r="F18" s="3">
         <f>SUM(D18:E18)</f>
         <v>8690</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B23" s="4">
+      <c r="B23" s="2">
         <v>1</v>
       </c>
-      <c r="C23" s="7">
+      <c r="C23" s="5">
         <v>0.01</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B24" s="4">
+      <c r="B24" s="2">
         <v>5</v>
       </c>
-      <c r="C24" s="7">
+      <c r="C24" s="5">
         <v>0.03</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B25" s="4">
+      <c r="B25" s="2">
         <v>10</v>
       </c>
-      <c r="C25" s="7">
+      <c r="C25" s="5">
         <v>0.05</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B26" s="4">
+      <c r="B26" s="2">
         <v>15</v>
       </c>
-      <c r="C26" s="7">
+      <c r="C26" s="5">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B27" s="4">
+      <c r="B27" s="2">
         <v>20</v>
       </c>
-      <c r="C27" s="7">
+      <c r="C27" s="5">
         <v>0.1</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B28" s="4">
+      <c r="B28" s="2">
         <v>25</v>
       </c>
-      <c r="C28" s="7">
+      <c r="C28" s="5">
         <v>0.15</v>
       </c>
     </row>
@@ -3732,404 +3757,404 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
     </row>
     <row r="3" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="4" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="4">
+      <c r="A4" s="2">
         <v>1</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D4" s="14">
+      <c r="D4" s="11">
         <f xml:space="preserve"> HLOOKUP(C4,$C$15:$G$20,3)</f>
         <v>130</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F4" s="12">
+      <c r="F4" s="9">
         <f xml:space="preserve"> D4*VLOOKUP(E4,$B$23:$C$25,2)</f>
         <v>4674.8</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="4">
+      <c r="A5" s="2">
         <v>2</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D5" s="14">
-        <f t="shared" ref="D5:D13" si="0" xml:space="preserve"> HLOOKUP(C5,$C$15:$G$20,3)</f>
+      <c r="D5" s="11">
+        <f t="shared" ref="D5" si="0" xml:space="preserve"> HLOOKUP(C5,$C$15:$G$20,3)</f>
         <v>145</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F5" s="12">
+      <c r="F5" s="9">
         <f t="shared" ref="F5:F13" si="1" xml:space="preserve"> D5*VLOOKUP(E5,$B$23:$C$25,2)</f>
         <v>5259.1500000000005</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="4">
+      <c r="A6" s="2">
         <v>3</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="11">
         <f xml:space="preserve"> HLOOKUP(C6,$C$15:$G$20,5)</f>
         <v>30</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F6" s="12">
+      <c r="F6" s="9">
         <f t="shared" si="1"/>
         <v>1088.1000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="4">
+      <c r="A7" s="2">
         <v>4</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="11">
         <f t="shared" ref="D7:D8" si="2" xml:space="preserve"> HLOOKUP(C7,$C$15:$G$20,5)</f>
         <v>25</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F7" s="12">
+      <c r="F7" s="9">
         <f t="shared" si="1"/>
         <v>906.75000000000011</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="4">
+      <c r="A8" s="2">
         <v>5</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="14">
+      <c r="D8" s="11">
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="9">
         <f t="shared" si="1"/>
         <v>1088.1000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="4">
+      <c r="A9" s="2">
         <v>6</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="14">
+      <c r="D9" s="11">
         <f xml:space="preserve"> HLOOKUP(C9,$C$15:$G$20,6)</f>
         <v>20</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="F9" s="12">
+      <c r="F9" s="9">
         <f t="shared" si="1"/>
         <v>719.2</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="4">
+      <c r="A10" s="2">
         <v>7</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="14">
+      <c r="D10" s="11">
         <f xml:space="preserve"> HLOOKUP(C10,$C$15:$G$20,6)</f>
         <v>17</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="F10" s="12">
+      <c r="F10" s="9">
         <f t="shared" si="1"/>
         <v>616.59</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="4">
+      <c r="A11" s="2">
         <v>8</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D11" s="14">
+      <c r="D11" s="11">
         <f xml:space="preserve"> HLOOKUP(C11,$C$15:$G$20,2)</f>
         <v>55</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="F11" s="12">
+      <c r="F11" s="9">
         <f t="shared" si="1"/>
         <v>1994.8500000000001</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="4">
+      <c r="A12" s="2">
         <v>9</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D12" s="14">
+      <c r="D12" s="11">
         <f xml:space="preserve"> HLOOKUP(C12,$C$15:$G$20,4)</f>
         <v>27</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="F12" s="12">
+      <c r="F12" s="9">
         <f t="shared" si="1"/>
         <v>979.29000000000008</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="4">
+      <c r="A13" s="2">
         <v>10</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="14">
+      <c r="D13" s="11">
         <f xml:space="preserve"> HLOOKUP(C13,$C$15:$G$20,4)</f>
         <v>22</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="F13" s="12">
+      <c r="F13" s="9">
         <f t="shared" si="1"/>
         <v>797.94</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="13" t="s">
+      <c r="B15" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="C15" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="D15" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="E15" s="13" t="s">
+      <c r="E15" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="F15" s="13" t="s">
+      <c r="F15" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="G15" s="13" t="s">
+      <c r="G15" s="10" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C16" s="11">
+      <c r="C16" s="8">
         <v>50</v>
       </c>
-      <c r="D16" s="11">
+      <c r="D16" s="8">
         <v>55</v>
       </c>
-      <c r="E16" s="11">
+      <c r="E16" s="8">
         <v>45</v>
       </c>
-      <c r="F16" s="11">
+      <c r="F16" s="8">
         <v>50</v>
       </c>
-      <c r="G16" s="11">
+      <c r="G16" s="8">
         <v>55</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C17" s="11">
+      <c r="C17" s="8">
         <v>150</v>
       </c>
-      <c r="D17" s="11">
+      <c r="D17" s="8">
         <v>130</v>
       </c>
-      <c r="E17" s="11">
+      <c r="E17" s="8">
         <v>140</v>
       </c>
-      <c r="F17" s="11">
+      <c r="F17" s="8">
         <v>145</v>
       </c>
-      <c r="G17" s="11">
+      <c r="G17" s="8">
         <v>155</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C18" s="11">
+      <c r="C18" s="8">
         <v>27</v>
       </c>
-      <c r="D18" s="11">
+      <c r="D18" s="8">
         <v>33</v>
       </c>
-      <c r="E18" s="11">
+      <c r="E18" s="8">
         <v>30</v>
       </c>
-      <c r="F18" s="11">
+      <c r="F18" s="8">
         <v>25</v>
       </c>
-      <c r="G18" s="11">
+      <c r="G18" s="8">
         <v>22</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C19" s="11">
+      <c r="C19" s="8">
         <v>25</v>
       </c>
-      <c r="D19" s="11">
+      <c r="D19" s="8">
         <v>30</v>
       </c>
-      <c r="E19" s="11">
+      <c r="E19" s="8">
         <v>30</v>
       </c>
-      <c r="F19" s="11">
+      <c r="F19" s="8">
         <v>35</v>
       </c>
-      <c r="G19" s="11">
+      <c r="G19" s="8">
         <v>30</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C20" s="11">
+      <c r="C20" s="8">
         <v>20</v>
       </c>
-      <c r="D20" s="11">
+      <c r="D20" s="8">
         <v>15</v>
       </c>
-      <c r="E20" s="11">
+      <c r="E20" s="8">
         <v>17</v>
       </c>
-      <c r="F20" s="11">
+      <c r="F20" s="8">
         <v>13</v>
       </c>
-      <c r="G20" s="11">
+      <c r="G20" s="8">
         <v>15</v>
       </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="9" t="s">
+      <c r="B22" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="C22" s="7" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C23" s="5">
+      <c r="C23" s="3">
         <v>35.42</v>
       </c>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C24" s="5">
+      <c r="C24" s="3">
         <v>35.96</v>
       </c>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C25" s="5">
+      <c r="C25" s="3">
         <v>36.270000000000003</v>
       </c>
     </row>
@@ -4155,233 +4180,233 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="B2" s="19">
+      <c r="B2" s="15">
         <v>1</v>
       </c>
-      <c r="C2" s="19">
+      <c r="C2" s="15">
         <v>2</v>
       </c>
-      <c r="D2" s="19">
+      <c r="D2" s="15">
         <v>3</v>
       </c>
-      <c r="E2" s="19">
+      <c r="E2" s="15">
         <v>4</v>
       </c>
-      <c r="F2" s="19">
+      <c r="F2" s="15">
         <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="B3" s="21">
+      <c r="B3" s="17">
         <v>1300</v>
       </c>
-      <c r="C3" s="21">
+      <c r="C3" s="17">
         <v>1400</v>
       </c>
-      <c r="D3" s="21">
+      <c r="D3" s="17">
         <v>1500</v>
       </c>
-      <c r="E3" s="21">
+      <c r="E3" s="17">
         <v>1700</v>
       </c>
-      <c r="F3" s="21">
+      <c r="F3" s="17">
         <v>2000</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="B4" s="18">
+      <c r="B4" s="14">
         <v>2000</v>
       </c>
-      <c r="C4" s="18">
+      <c r="C4" s="14">
         <v>2300</v>
       </c>
-      <c r="D4" s="18">
+      <c r="D4" s="14">
         <v>2500</v>
       </c>
-      <c r="E4" s="18">
+      <c r="E4" s="14">
         <v>3000</v>
       </c>
-      <c r="F4" s="18">
+      <c r="F4" s="14">
         <v>3500</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="28" t="s">
         <v>56</v>
       </c>
-      <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="15"/>
+      <c r="B6" s="28"/>
+      <c r="C6" s="28"/>
+      <c r="D6" s="28"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="28"/>
     </row>
     <row r="8" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="4" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="16" t="s">
+      <c r="A9" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="16">
+      <c r="B9" s="12">
         <v>22</v>
       </c>
-      <c r="C9" s="16">
+      <c r="C9" s="12">
         <v>2</v>
       </c>
-      <c r="D9" s="22">
+      <c r="D9" s="18">
         <f xml:space="preserve"> HLOOKUP(C9,B$2:F$4,2)*B9</f>
         <v>30800</v>
       </c>
-      <c r="E9" s="22">
+      <c r="E9" s="18">
         <f xml:space="preserve"> HLOOKUP(C9,B$2:F$4,3)</f>
         <v>2300</v>
       </c>
-      <c r="F9" s="22">
+      <c r="F9" s="18">
         <f>SUM(D9:E9)</f>
         <v>33100</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="16" t="s">
+      <c r="A10" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="B10" s="16">
+      <c r="B10" s="12">
         <v>18</v>
       </c>
-      <c r="C10" s="16">
+      <c r="C10" s="12">
         <v>3</v>
       </c>
-      <c r="D10" s="22">
+      <c r="D10" s="18">
         <f t="shared" ref="D10:D13" si="0" xml:space="preserve"> HLOOKUP(C10,B$2:F$4,2)*B10</f>
         <v>27000</v>
       </c>
-      <c r="E10" s="22">
+      <c r="E10" s="18">
         <f t="shared" ref="E10:E12" si="1" xml:space="preserve"> HLOOKUP(C10,B$2:F$4,3)</f>
         <v>2500</v>
       </c>
-      <c r="F10" s="22">
+      <c r="F10" s="18">
         <f t="shared" ref="F10:F13" si="2">SUM(D10:E10)</f>
         <v>29500</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="16" t="s">
+      <c r="A11" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="16">
+      <c r="B11" s="12">
         <v>21</v>
       </c>
-      <c r="C11" s="16">
+      <c r="C11" s="12">
         <v>4</v>
       </c>
-      <c r="D11" s="22">
+      <c r="D11" s="18">
         <f t="shared" si="0"/>
         <v>35700</v>
       </c>
-      <c r="E11" s="22">
+      <c r="E11" s="18">
         <f t="shared" si="1"/>
         <v>3000</v>
       </c>
-      <c r="F11" s="22">
+      <c r="F11" s="18">
         <f t="shared" si="2"/>
         <v>38700</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="16" t="s">
+      <c r="A12" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="16">
+      <c r="B12" s="12">
         <v>21</v>
       </c>
-      <c r="C12" s="16">
+      <c r="C12" s="12">
         <v>3</v>
       </c>
-      <c r="D12" s="22">
+      <c r="D12" s="18">
         <f t="shared" si="0"/>
         <v>31500</v>
       </c>
-      <c r="E12" s="22">
+      <c r="E12" s="18">
         <f t="shared" si="1"/>
         <v>2500</v>
       </c>
-      <c r="F12" s="22">
+      <c r="F12" s="18">
         <f t="shared" si="2"/>
         <v>34000</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="16" t="s">
+      <c r="A13" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="B13" s="16">
+      <c r="B13" s="12">
         <v>15</v>
       </c>
-      <c r="C13" s="23">
+      <c r="C13" s="19">
         <v>5</v>
       </c>
-      <c r="D13" s="24">
+      <c r="D13" s="20">
         <f t="shared" si="0"/>
         <v>30000</v>
       </c>
-      <c r="E13" s="24">
+      <c r="E13" s="20">
         <f xml:space="preserve"> HLOOKUP(C13,B$2:F$4,3)</f>
         <v>3500</v>
       </c>
-      <c r="F13" s="24">
+      <c r="F13" s="20">
         <f t="shared" si="2"/>
         <v>33500</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C14" s="25" t="s">
+      <c r="C14" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="D14" s="26">
+      <c r="D14" s="22">
         <f>SUM(D9:D13)</f>
         <v>155000</v>
       </c>
-      <c r="E14" s="26">
+      <c r="E14" s="22">
         <f t="shared" ref="E14:F14" si="3">SUM(E9:E13)</f>
         <v>13800</v>
       </c>
-      <c r="F14" s="26">
+      <c r="F14" s="22">
         <f t="shared" si="3"/>
         <v>168800</v>
       </c>
@@ -4409,229 +4434,229 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="29" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3" s="3">
         <v>0</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3" s="3">
         <v>10000</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3" s="3">
         <v>18000</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="3">
         <v>25000</v>
       </c>
-      <c r="F3" s="5">
+      <c r="F3" s="3">
         <v>30000</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="5">
         <v>0</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="5">
         <v>0.12</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="5">
         <v>0.13</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="5">
         <v>0.15</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="5">
         <v>0.18</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="3">
         <v>1400</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="B7" s="15"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="15"/>
+      <c r="B7" s="28"/>
+      <c r="C7" s="28"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
     </row>
     <row r="9" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="27" t="s">
+      <c r="A9" s="23" t="s">
         <v>73</v>
       </c>
-      <c r="B9" s="27" t="s">
+      <c r="B9" s="23" t="s">
         <v>69</v>
       </c>
-      <c r="C9" s="27" t="s">
+      <c r="C9" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="D9" s="27" t="s">
+      <c r="D9" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="E9" s="27" t="s">
+      <c r="E9" s="23" t="s">
         <v>66</v>
       </c>
-      <c r="F9" s="27" t="s">
+      <c r="F9" s="23" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="16" t="s">
+      <c r="A10" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="4">
+      <c r="B10" s="2">
         <v>0</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C10" s="3">
         <v>12000</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10" s="3">
         <f>MAX(0,C10 - B10*$B$5)</f>
         <v>12000</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="3">
         <f>HLOOKUP(D10,$B$3:$F$4,2)*D10</f>
         <v>1440</v>
       </c>
-      <c r="F10" s="5">
+      <c r="F10" s="3">
         <f>SUM(C10:E10)</f>
         <v>25440</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="16" t="s">
+      <c r="A11" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="B11" s="4">
+      <c r="B11" s="2">
         <v>1</v>
       </c>
-      <c r="C11" s="5">
+      <c r="C11" s="3">
         <v>18400</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D11" s="3">
         <f t="shared" ref="D11:D14" si="0">MAX(0,C11 - B11*$B$5)</f>
         <v>17000</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11" s="3">
         <f t="shared" ref="E11:E14" si="1">HLOOKUP(D11,$B$3:$F$4,2)*D11</f>
         <v>2040</v>
       </c>
-      <c r="F11" s="5">
+      <c r="F11" s="3">
         <f t="shared" ref="F11:F14" si="2">SUM(C11:E11)</f>
         <v>37440</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="16" t="s">
+      <c r="A12" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="4">
+      <c r="B12" s="2">
         <v>2</v>
       </c>
-      <c r="C12" s="5">
+      <c r="C12" s="3">
         <v>15600</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D12" s="3">
         <f t="shared" si="0"/>
         <v>12800</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12" s="3">
         <f t="shared" si="1"/>
         <v>1536</v>
       </c>
-      <c r="F12" s="5">
+      <c r="F12" s="3">
         <f t="shared" si="2"/>
         <v>29936</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="16" t="s">
+      <c r="A13" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="4">
+      <c r="B13" s="2">
         <v>2</v>
       </c>
-      <c r="C13" s="5">
+      <c r="C13" s="3">
         <v>22540</v>
       </c>
-      <c r="D13" s="5">
+      <c r="D13" s="3">
         <f t="shared" si="0"/>
         <v>19740</v>
       </c>
-      <c r="E13" s="5">
+      <c r="E13" s="3">
         <f t="shared" si="1"/>
         <v>2566.2000000000003</v>
       </c>
-      <c r="F13" s="5">
+      <c r="F13" s="3">
         <f t="shared" si="2"/>
         <v>44846.2</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="16" t="s">
+      <c r="A14" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="B14" s="4">
+      <c r="B14" s="2">
         <v>3</v>
       </c>
-      <c r="C14" s="5">
+      <c r="C14" s="3">
         <v>29500</v>
       </c>
-      <c r="D14" s="5">
+      <c r="D14" s="3">
         <f t="shared" si="0"/>
         <v>25300</v>
       </c>
-      <c r="E14" s="5">
+      <c r="E14" s="3">
         <f t="shared" si="1"/>
         <v>3795</v>
       </c>
-      <c r="F14" s="5">
+      <c r="F14" s="3">
         <f t="shared" si="2"/>
         <v>58595</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="28" t="s">
+      <c r="A15" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="B15" s="25">
+      <c r="B15" s="21">
         <f>SUM(B10:B14)</f>
         <v>8</v>
       </c>
-      <c r="C15" s="29">
+      <c r="C15" s="25">
         <f t="shared" ref="C15:F15" si="3">SUM(C10:C14)</f>
         <v>98040</v>
       </c>
-      <c r="D15" s="29">
+      <c r="D15" s="25">
         <f t="shared" si="3"/>
         <v>86840</v>
       </c>
-      <c r="E15" s="29">
+      <c r="E15" s="25">
         <f t="shared" si="3"/>
         <v>11377.2</v>
       </c>
-      <c r="F15" s="29">
+      <c r="F15" s="25">
         <f t="shared" si="3"/>
         <v>196257.2</v>
       </c>
